--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2020_la_araucania_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2020_la_araucania_provincial.xlsx
@@ -46,7 +46,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:11</t>
+    <t xml:space="preserve">2026-09-29 14:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2020_la_araucania_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2020_la_araucania_provincial.xlsx
@@ -46,7 +46,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 14:08</t>
+    <t xml:space="preserve">2026-09-29 18:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2020_la_araucania_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2020_la_araucania_provincial.xlsx
@@ -46,7 +46,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 18:39</t>
+    <t xml:space="preserve">2026-10-05 04:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -487,10 +487,10 @@
         <v>10.74</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>34.12</v>
+        <v>34.13</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>23.38</v>
+        <v>23.39</v>
       </c>
     </row>
     <row r="3">
